--- a/artfynd/A 2534-2024 artfynd.xlsx
+++ b/artfynd/A 2534-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Cajsa Björkén, Gillis Aronsson, Helena Björnström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 2534-2024 artfynd.xlsx
+++ b/artfynd/A 2534-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120220704</v>
       </c>
       <c r="B2" t="n">
-        <v>104970</v>
+        <v>104993</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2024 artfynd.xlsx
+++ b/artfynd/A 2534-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>122354573</v>
       </c>
       <c r="B3" t="n">
-        <v>105241</v>
+        <v>105251</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2024 artfynd.xlsx
+++ b/artfynd/A 2534-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>122354573</v>
       </c>
       <c r="B3" t="n">
-        <v>105251</v>
+        <v>105264</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2024 artfynd.xlsx
+++ b/artfynd/A 2534-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>122354573</v>
       </c>
       <c r="B3" t="n">
-        <v>105264</v>
+        <v>105269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2024 artfynd.xlsx
+++ b/artfynd/A 2534-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>122354573</v>
       </c>
       <c r="B3" t="n">
-        <v>105269</v>
+        <v>105278</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,11 +818,6 @@
       </c>
       <c r="E3" t="n">
         <v>340</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Ryl</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2024 artfynd.xlsx
+++ b/artfynd/A 2534-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>122354573</v>
       </c>
       <c r="B3" t="n">
-        <v>105278</v>
+        <v>105291</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,6 +818,11 @@
       </c>
       <c r="E3" t="n">
         <v>340</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ryl</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2024 artfynd.xlsx
+++ b/artfynd/A 2534-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>122354573</v>
       </c>
       <c r="B3" t="n">
-        <v>105291</v>
+        <v>105304</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2024 artfynd.xlsx
+++ b/artfynd/A 2534-2024 artfynd.xlsx
@@ -808,7 +808,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -841,9 +841,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Petesviken, Gtl</t>
@@ -904,6 +907,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2534-2024 artfynd.xlsx
+++ b/artfynd/A 2534-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>122354573</v>
       </c>
       <c r="B3" t="n">
-        <v>105304</v>
+        <v>105307</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2024 artfynd.xlsx
+++ b/artfynd/A 2534-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>122354573</v>
       </c>
       <c r="B3" t="n">
-        <v>105307</v>
+        <v>105308</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2024 artfynd.xlsx
+++ b/artfynd/A 2534-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>122354573</v>
       </c>
       <c r="B3" t="n">
-        <v>105308</v>
+        <v>105311</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2024 artfynd.xlsx
+++ b/artfynd/A 2534-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>122354573</v>
       </c>
       <c r="B3" t="n">
-        <v>105311</v>
+        <v>105414</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2024 artfynd.xlsx
+++ b/artfynd/A 2534-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>122354573</v>
       </c>
       <c r="B3" t="n">
-        <v>105414</v>
+        <v>105422</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2024 artfynd.xlsx
+++ b/artfynd/A 2534-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>122354573</v>
       </c>
       <c r="B3" t="n">
-        <v>105422</v>
+        <v>105424</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2024 artfynd.xlsx
+++ b/artfynd/A 2534-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>122354573</v>
       </c>
       <c r="B3" t="n">
-        <v>105424</v>
+        <v>105432</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
